--- a/CWEsIntroducedMapping/CWEMappings.xlsx
+++ b/CWEsIntroducedMapping/CWEMappings.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EducationalFiles\Massey\MInfSc\Re\Scenarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EducationalFiles\Massey\MInfSc\Re\Scenarios\CWEsIntroducedMapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B30902-1C26-49D9-8137-7876A90ADBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D5459FD-C915-4C39-87F0-997047FFAA73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13866" xr2:uid="{E9D892D6-17AD-44AD-B269-50B4899FCA39}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="35">
   <si>
     <t>GPT 4.1</t>
   </si>
@@ -515,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CAA1A9-DAE9-4C9F-9E85-849A6DE5A558}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="23.703125" customWidth="1"/>
@@ -594,40 +594,40 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A10" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>2</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="C11" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="C12" t="s">
         <v>3</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>4</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E12" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.5">
@@ -635,99 +635,99 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s">
         <v>15</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D14" t="s">
         <v>16</v>
       </c>
-      <c r="E13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A16" t="s">
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A17" t="s">
         <v>18</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
         <v>2</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C17" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="C17" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="C18" t="s">
         <v>3</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D18" t="s">
         <v>4</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E18" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="B18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.5">
       <c r="B19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
         <v>17</v>
       </c>
       <c r="E19" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.5">
       <c r="B20" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E20" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.5">
       <c r="B21" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.5">
       <c r="B22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D22" t="s">
         <v>8</v>
@@ -736,67 +736,81 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A25" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A26" t="s">
         <v>28</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B26" t="s">
         <v>2</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C26" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="C26" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="C27" t="s">
         <v>3</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D27" t="s">
         <v>4</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E27" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="B27" t="s">
-        <v>19</v>
-      </c>
-      <c r="C27" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.5">
       <c r="B28" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C28" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E28" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="B29" s="1" t="s">
+      <c r="B29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="B30" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C30" t="s">
         <v>8</v>
       </c>
-      <c r="D29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="D30" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s">
         <v>32</v>
       </c>
     </row>

--- a/CWEsIntroducedMapping/CWEMappings.xlsx
+++ b/CWEsIntroducedMapping/CWEMappings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EducationalFiles\Massey\MInfSc\Re\Scenarios\CWEsIntroducedMapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D5459FD-C915-4C39-87F0-997047FFAA73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3363576C-CD53-45B2-8969-82D0E3263752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13866" xr2:uid="{E9D892D6-17AD-44AD-B269-50B4899FCA39}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="34">
   <si>
     <t>GPT 4.1</t>
   </si>
@@ -132,9 +132,6 @@
   </si>
   <si>
     <t>[502], [79, 116]</t>
-  </si>
-  <si>
-    <t>xx</t>
   </si>
   <si>
     <t>Python</t>
@@ -527,7 +524,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.5">
@@ -554,7 +551,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.5">
       <c r="B5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
@@ -783,7 +780,7 @@
         <v>17</v>
       </c>
       <c r="E28" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.5">
@@ -797,7 +794,7 @@
         <v>9</v>
       </c>
       <c r="E29" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.5">
@@ -811,7 +808,7 @@
         <v>17</v>
       </c>
       <c r="E30" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
